--- a/InputData/elec/MABAaSoF/Max Annual Buildable Additions as Share of Fleet.xlsx
+++ b/InputData/elec/MABAaSoF/Max Annual Buildable Additions as Share of Fleet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-dev-sandbox\InputData\elec\MABAaSoF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-analysis\InputData\elec\MABAaSoF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8667A6B-1C6E-4AE1-B402-6F59B56C2F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E05C5D-90AB-480E-943F-31A7C9FECFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="26640" windowHeight="15615" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -106,16 +106,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,7 +419,7 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
@@ -430,7 +428,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
@@ -438,27 +436,27 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -492,7 +490,7 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
